--- a/EXCEL/class notes/day13 error handling/Error Handing_V1.xlsx
+++ b/EXCEL/class notes/day13 error handling/Error Handing_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day13 error handling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{800DFFAE-AB2B-4EF0-BCB7-210445F132C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCF6245-473E-418A-8E1E-34FF9B2F9208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{71259DAE-1C4C-4155-A095-A22735B4E5E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{71259DAE-1C4C-4155-A095-A22735B4E5E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -526,17 +535,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC896CC-2761-4FDD-9016-9987832CD9A6}">
   <dimension ref="B4:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
@@ -550,7 +559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2</v>
       </c>
@@ -558,7 +567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>3</v>
       </c>
@@ -578,7 +587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I9" t="s">
         <v>9</v>
       </c>
@@ -586,7 +595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>4</v>
       </c>
@@ -594,7 +603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>7</v>
       </c>
@@ -615,7 +624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="F13" t="s">
         <v>8</v>
       </c>
@@ -636,18 +645,18 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G16" s="2" t="b">
         <f>ISERROR(G13)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19" s="6" t="str">
         <f>IF(ISERROR(G6/G8),"B value is zero",G6/G8)</f>
         <v>B value is zero</v>
@@ -661,12 +670,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68675136-D7D3-45B5-8135-B915DC8FA071}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -677,7 +686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -686,10 +695,10 @@
       </c>
       <c r="C2" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -697,8 +706,8 @@
         <v>18</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C16" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>90</v>
+        <f t="shared" ref="C3:C7" ca="1" si="0">RANDBETWEEN(1,100)</f>
+        <v>26</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>14</v>
@@ -710,7 +719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -719,7 +728,7 @@
       </c>
       <c r="C4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>14</v>
@@ -737,11 +746,11 @@
         <v>23</v>
       </c>
       <c r="M4" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ref="M4:M12" ca="1" si="1">RANDBETWEEN(1,100)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1004</v>
       </c>
@@ -750,18 +759,18 @@
       </c>
       <c r="C5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3">
         <v>1009</v>
       </c>
       <c r="G5" s="5" t="str">
-        <f>IF(ISERROR(VLOOKUP($F5,$A$1:$C$7,2,0)),"Not Availble",VLOOKUP($F5,$A$1:$C$7,2,0))</f>
-        <v>Not Availble</v>
-      </c>
-      <c r="H5" s="5" t="str">
-        <f>IF(ISERROR(VLOOKUP($F5,$A$1:$C$7,3,0)),"Not Availble",VLOOKUP($F5,$A$1:$C$7,3,0))</f>
-        <v>Not Availble</v>
+        <f>IF(ISERROR(VLOOKUP($F5,$A$1:$C$7,2,0)),VLOOKUP($F5,$K$3:$M$12,2,0),VLOOKUP($F5,$A$1:$C$7,2,0))</f>
+        <v>Nme9</v>
+      </c>
+      <c r="H5" s="5">
+        <f ca="1">IF(ISERROR(VLOOKUP($F5,$A$1:$C$7,3,0)),VLOOKUP($F5,$K$3:$M$12,3,0),VLOOKUP($F5,$A$1:$C$7,3,0))</f>
+        <v>39</v>
       </c>
       <c r="K5" s="3">
         <v>1008</v>
@@ -770,11 +779,11 @@
         <v>24</v>
       </c>
       <c r="M5" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
@@ -783,18 +792,18 @@
       </c>
       <c r="C6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>1003</v>
       </c>
       <c r="G6" s="5" t="str">
-        <f t="shared" ref="G6:G19" si="1">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,2,0)),"Not Availble",VLOOKUP($F6,$A$1:$C$7,2,0))</f>
+        <f t="shared" ref="G6:G19" si="2">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,2,0)),VLOOKUP($F6,$K$3:$M$12,2,0),VLOOKUP($F6,$A$1:$C$7,2,0))</f>
         <v>Nme3</v>
       </c>
       <c r="H6" s="5">
-        <f t="shared" ref="H6:H19" ca="1" si="2">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,3,0)),"Not Availble",VLOOKUP($F6,$A$1:$C$7,3,0))</f>
-        <v>100</v>
+        <f t="shared" ref="H6:H19" ca="1" si="3">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,3,0)),VLOOKUP($F6,$K$3:$M$12,3,0),VLOOKUP($F6,$A$1:$C$7,3,0))</f>
+        <v>1</v>
       </c>
       <c r="K6" s="3">
         <v>1009</v>
@@ -803,11 +812,11 @@
         <v>25</v>
       </c>
       <c r="M6" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1006</v>
       </c>
@@ -816,18 +825,18 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3">
         <v>1004</v>
       </c>
       <c r="G7" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme4</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>47</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>74</v>
       </c>
       <c r="K7" s="3">
         <v>1010</v>
@@ -836,21 +845,21 @@
         <v>26</v>
       </c>
       <c r="M7" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F8" s="3">
         <v>1012</v>
       </c>
       <c r="G8" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H8" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
+        <f t="shared" si="2"/>
+        <v>Nme12</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
       <c r="K8" s="3">
         <v>1011</v>
@@ -859,21 +868,21 @@
         <v>27</v>
       </c>
       <c r="M8" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F9" s="3">
         <v>1015</v>
       </c>
       <c r="G9" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H9" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
+        <f t="shared" si="2"/>
+        <v>Nme15</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>80</v>
       </c>
       <c r="K9" s="3">
         <v>1012</v>
@@ -882,21 +891,21 @@
         <v>28</v>
       </c>
       <c r="M9" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F10" s="3">
         <v>1013</v>
       </c>
       <c r="G10" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H10" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
+        <f t="shared" si="2"/>
+        <v>Nme13</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>53</v>
       </c>
       <c r="K10" s="3">
         <v>1013</v>
@@ -905,21 +914,21 @@
         <v>29</v>
       </c>
       <c r="M10" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F11" s="3">
         <v>1014</v>
       </c>
       <c r="G11" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H11" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
+        <f t="shared" si="2"/>
+        <v>Nme14</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>83</v>
       </c>
       <c r="K11" s="3">
         <v>1014</v>
@@ -928,21 +937,21 @@
         <v>30</v>
       </c>
       <c r="M11" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F12" s="3">
         <v>1001</v>
       </c>
       <c r="G12" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme1</v>
       </c>
       <c r="H12" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>33</v>
       </c>
       <c r="K12" s="3">
         <v>1015</v>
@@ -951,99 +960,99 @@
         <v>31</v>
       </c>
       <c r="M12" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F13" s="3">
         <v>1007</v>
       </c>
       <c r="G13" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H13" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Nme7</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F14" s="3">
         <v>1010</v>
       </c>
       <c r="G14" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H14" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Nme10</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F15" s="3">
         <v>1006</v>
       </c>
       <c r="G15" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme6</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="3"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F16" s="3">
         <v>1008</v>
       </c>
       <c r="G16" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H16" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
-      </c>
-    </row>
-    <row r="17" spans="6:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Nme8</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F17" s="3">
         <v>1002</v>
       </c>
       <c r="G17" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme2</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="6:8" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F18" s="3">
         <v>1005</v>
       </c>
       <c r="G18" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme5</v>
       </c>
       <c r="H18" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="6:8" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F19" s="3">
         <v>1011</v>
       </c>
       <c r="G19" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Availble</v>
-      </c>
-      <c r="H19" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>Not Availble</v>
+        <f t="shared" si="2"/>
+        <v>Nme11</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1058,12 +1067,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5592640-6062-4FE4-8B58-627DD6CBD696}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -1074,7 +1083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1083,10 +1092,10 @@
       </c>
       <c r="C2" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -1094,8 +1103,8 @@
         <v>18</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C16" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>10</v>
+        <f t="shared" ref="C3:C7" ca="1" si="0">RANDBETWEEN(1,100)</f>
+        <v>32</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>14</v>
@@ -1107,7 +1116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -1116,7 +1125,7 @@
       </c>
       <c r="C4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>14</v>
@@ -1134,11 +1143,11 @@
         <v>23</v>
       </c>
       <c r="M4" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ref="M4:M12" ca="1" si="1">RANDBETWEEN(1,100)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1004</v>
       </c>
@@ -1147,7 +1156,7 @@
       </c>
       <c r="C5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3">
         <v>1009</v>
@@ -1167,11 +1176,11 @@
         <v>24</v>
       </c>
       <c r="M5" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
@@ -1180,17 +1189,17 @@
       </c>
       <c r="C6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" s="3">
         <v>1003</v>
       </c>
       <c r="G6" s="5" t="str">
-        <f t="shared" ref="G6:H19" si="1">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,2,0)),VLOOKUP($F6,$K$3:$M$12,2,0),VLOOKUP($F6,$A$1:$C$7,2,0))</f>
+        <f t="shared" ref="G6:H19" si="2">IF(ISERROR(VLOOKUP($F6,$A$1:$C$7,2,0)),VLOOKUP($F6,$K$3:$M$12,2,0),VLOOKUP($F6,$A$1:$C$7,2,0))</f>
         <v>Nme3</v>
       </c>
       <c r="H6" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme3</v>
       </c>
       <c r="K6" s="3">
@@ -1200,11 +1209,11 @@
         <v>25</v>
       </c>
       <c r="M6" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1006</v>
       </c>
@@ -1213,17 +1222,17 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3">
         <v>1004</v>
       </c>
       <c r="G7" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme4</v>
       </c>
       <c r="H7" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme4</v>
       </c>
       <c r="K7" s="3">
@@ -1233,20 +1242,20 @@
         <v>26</v>
       </c>
       <c r="M7" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F8" s="3">
         <v>1012</v>
       </c>
       <c r="G8" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme12</v>
       </c>
       <c r="H8" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme12</v>
       </c>
       <c r="K8" s="3">
@@ -1256,20 +1265,20 @@
         <v>27</v>
       </c>
       <c r="M8" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F9" s="3">
         <v>1015</v>
       </c>
       <c r="G9" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme15</v>
       </c>
       <c r="H9" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme15</v>
       </c>
       <c r="K9" s="3">
@@ -1279,20 +1288,20 @@
         <v>28</v>
       </c>
       <c r="M9" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F10" s="3">
         <v>1013</v>
       </c>
       <c r="G10" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme13</v>
       </c>
       <c r="H10" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme13</v>
       </c>
       <c r="K10" s="3">
@@ -1302,20 +1311,20 @@
         <v>29</v>
       </c>
       <c r="M10" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F11" s="3">
         <v>1014</v>
       </c>
       <c r="G11" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme14</v>
       </c>
       <c r="H11" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme14</v>
       </c>
       <c r="K11" s="3">
@@ -1325,20 +1334,20 @@
         <v>30</v>
       </c>
       <c r="M11" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F12" s="3">
         <v>1001</v>
       </c>
       <c r="G12" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme1</v>
       </c>
       <c r="H12" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme1</v>
       </c>
       <c r="K12" s="3">
@@ -1348,98 +1357,98 @@
         <v>31</v>
       </c>
       <c r="M12" s="3">
-        <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F13" s="3">
         <v>1007</v>
       </c>
       <c r="G13" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme7</v>
       </c>
       <c r="H13" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme7</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F14" s="3">
         <v>1010</v>
       </c>
       <c r="G14" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme10</v>
       </c>
       <c r="H14" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F15" s="3">
         <v>1006</v>
       </c>
       <c r="G15" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme6</v>
       </c>
       <c r="H15" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F16" s="3">
         <v>1008</v>
       </c>
       <c r="G16" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme8</v>
       </c>
       <c r="H16" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme8</v>
       </c>
     </row>
-    <row r="17" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F17" s="3">
         <v>1002</v>
       </c>
       <c r="G17" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme2</v>
       </c>
       <c r="H17" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme2</v>
       </c>
     </row>
-    <row r="18" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F18" s="3">
         <v>1005</v>
       </c>
       <c r="G18" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme5</v>
       </c>
       <c r="H18" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme5</v>
       </c>
     </row>
-    <row r="19" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F19" s="3">
         <v>1011</v>
       </c>
       <c r="G19" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme11</v>
       </c>
       <c r="H19" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Nme11</v>
       </c>
     </row>
